--- a/kb/Human validated 50 questions.xlsx
+++ b/kb/Human validated 50 questions.xlsx
@@ -625,7 +625,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -663,7 +663,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -684,6 +684,13 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -707,8 +714,8 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -738,7 +745,7 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1047,7 +1054,7 @@
   <cols>
     <col min="1" max="1" style="15" width="5.147857142857143" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="16" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="50.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="74.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="16" width="156.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="16" width="97.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="16" width="69.005" customWidth="1" bestFit="1"/>
@@ -1165,7 +1172,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="30.75" customFormat="1" s="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1501,7 +1508,7 @@
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="102" customFormat="1" s="1">
       <c r="A29" s="9">
         <v>28</v>
       </c>
@@ -1517,7 +1524,7 @@
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="102" customFormat="1" s="1">
       <c r="A30" s="9">
         <v>29</v>
       </c>
@@ -1533,7 +1540,7 @@
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="60.75" customFormat="1" s="1">
       <c r="A31" s="9">
         <v>30</v>
       </c>
@@ -1549,7 +1556,7 @@
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="171" customFormat="1" s="1">
       <c r="A32" s="9">
         <v>31</v>
       </c>
@@ -1565,7 +1572,7 @@
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="60.75" customFormat="1" s="1">
       <c r="A33" s="9">
         <v>32</v>
       </c>
@@ -1581,7 +1588,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="432" customFormat="1" s="1">
       <c r="A34" s="9">
         <v>33</v>
       </c>
@@ -1597,7 +1604,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="171" customFormat="1" s="1">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -1613,7 +1620,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="88.5" customFormat="1" s="1">
       <c r="A36" s="11">
         <v>35</v>
       </c>
@@ -1629,7 +1636,7 @@
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="115.5" customFormat="1" s="1">
       <c r="A37" s="11">
         <v>36</v>
       </c>
@@ -1645,7 +1652,7 @@
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="60.75" customFormat="1" s="1">
       <c r="A38" s="11">
         <v>37</v>
       </c>
@@ -1661,7 +1668,7 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="60.75" customFormat="1" s="1">
       <c r="A39" s="11">
         <v>38</v>
       </c>
@@ -1677,7 +1684,7 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="74.25" customFormat="1" s="1">
       <c r="A40" s="11">
         <v>39</v>
       </c>
@@ -1693,7 +1700,7 @@
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="88.5" customFormat="1" s="1">
       <c r="A41" s="11">
         <v>40</v>
       </c>
@@ -1709,7 +1716,7 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="102" customFormat="1" s="1">
       <c r="A42" s="11">
         <v>41</v>
       </c>
@@ -1725,7 +1732,7 @@
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="88.5" customFormat="1" s="1">
       <c r="A43" s="11">
         <v>42</v>
       </c>
@@ -1741,7 +1748,7 @@
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="60.75" customFormat="1" s="1">
       <c r="A44" s="11">
         <v>43</v>
       </c>
@@ -1757,7 +1764,7 @@
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="47.25" customFormat="1" s="1">
       <c r="A45" s="11">
         <v>44</v>
       </c>
@@ -1773,7 +1780,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="88.5" customFormat="1" s="1">
       <c r="A46" s="11">
         <v>45</v>
       </c>
@@ -1789,7 +1796,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="74.25" customFormat="1" s="1">
       <c r="A47" s="13">
         <v>46</v>
       </c>

--- a/kb/Human validated 50 questions.xlsx
+++ b/kb/Human validated 50 questions.xlsx
@@ -1076,7 +1076,7 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="237" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="276" customFormat="1" s="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1092,7 +1092,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="114" customFormat="1" s="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1108,7 +1108,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="87" customFormat="1" s="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1124,7 +1124,7 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="73.5" customFormat="1" s="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1140,7 +1140,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="168" customFormat="1" s="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1156,7 +1156,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1172,7 +1172,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="30.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1188,7 +1188,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1204,7 +1204,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1220,7 +1220,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="154.5" customFormat="1" s="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1236,7 +1236,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="60" customFormat="1" s="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -1252,7 +1252,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="73.5" customFormat="1" s="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1268,7 +1268,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="100.5" customFormat="1" s="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1284,7 +1284,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="73.5" customFormat="1" s="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1316,7 +1316,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -1332,7 +1332,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="60" customFormat="1" s="1">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -1348,7 +1348,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -1364,7 +1364,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -1380,7 +1380,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -1396,7 +1396,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="181.5" customFormat="1" s="1">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -1412,7 +1412,7 @@
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="73.5" customFormat="1" s="1">
       <c r="A23" s="7">
         <v>22</v>
       </c>
@@ -1428,7 +1428,7 @@
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A24" s="7">
         <v>23</v>
       </c>
@@ -1444,7 +1444,7 @@
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="114" customFormat="1" s="1">
       <c r="A25" s="7">
         <v>24</v>
       </c>
@@ -1460,7 +1460,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="141" customFormat="1" s="1">
       <c r="A26" s="7">
         <v>25</v>
       </c>

--- a/kb/Human validated 50 questions.xlsx
+++ b/kb/Human validated 50 questions.xlsx
@@ -571,7 +571,7 @@
     <t>Covington, Henry County has 2 Materials‑category suppliers that could support battery thermal management production for a new Tier 1 company in Georgia.</t>
   </si>
   <si>
-    <t>How many Georgia areas have concentrated Manufacturing Plant facilities but no EV-specific production presence, indicating potential conversion-ready industrial sites?</t>
+    <t>Which Georgia areas have concentrated Manufacturing Plant facilities that already supply the EV chain indirectly but have no dedicated EV production yet,  marking them as prime conversion candidates?</t>
   </si>
   <si>
     <t>There are 100 Georgia areas that currently host Manufacturing Plant facilities but have no EV‑specific production presence, indicating a large pool of potentially conversion‑ready industrial sites.
@@ -1076,7 +1076,7 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="276" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="261.75" customFormat="1" s="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>

--- a/kb/Human validated 50 questions.xlsx
+++ b/kb/Human validated 50 questions.xlsx
@@ -1060,7 +1060,7 @@
     <col min="6" max="6" style="16" width="69.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="31.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1076,7 +1076,7 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="261.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="276" customFormat="1" s="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1588,7 +1588,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="432" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="424.5" customFormat="1" s="1">
       <c r="A34" s="9">
         <v>33</v>
       </c>
@@ -1604,7 +1604,7 @@
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="171" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="168" customFormat="1" s="1">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="88.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="87" customFormat="1" s="1">
       <c r="A36" s="11">
         <v>35</v>
       </c>

--- a/kb/Human validated 50 questions.xlsx
+++ b/kb/Human validated 50 questions.xlsx
@@ -1060,7 +1060,7 @@
     <col min="6" max="6" style="16" width="69.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="31.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="33" customFormat="1" s="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
